--- a/PROMISER/configurations/logcats_DTB_2025.xlsx
+++ b/PROMISER/configurations/logcats_DTB_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF366"/>
+  <dimension ref="A1:BG366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -723,6 +723,11 @@
           <t>Gigs.Retail</t>
         </is>
       </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>Goods.Sellers</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -899,6 +904,9 @@
       <c r="BF2" t="n">
         <v>0</v>
       </c>
+      <c r="BG2" t="n">
+        <v>301478</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -1075,6 +1083,9 @@
       <c r="BF3" t="n">
         <v>0</v>
       </c>
+      <c r="BG3" t="n">
+        <v>492385</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -1251,6 +1262,9 @@
       <c r="BF4" t="n">
         <v>0</v>
       </c>
+      <c r="BG4" t="n">
+        <v>554873</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -1427,6 +1441,9 @@
       <c r="BF5" t="n">
         <v>0</v>
       </c>
+      <c r="BG5" t="n">
+        <v>573628</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -1603,6 +1620,9 @@
       <c r="BF6" t="n">
         <v>0</v>
       </c>
+      <c r="BG6" t="n">
+        <v>633044</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -1779,6 +1799,9 @@
       <c r="BF7" t="n">
         <v>0</v>
       </c>
+      <c r="BG7" t="n">
+        <v>629424</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -1955,6 +1978,9 @@
       <c r="BF8" t="n">
         <v>0</v>
       </c>
+      <c r="BG8" t="n">
+        <v>598749</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -2131,6 +2157,9 @@
       <c r="BF9" t="n">
         <v>0</v>
       </c>
+      <c r="BG9" t="n">
+        <v>688617</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -2307,6 +2336,9 @@
       <c r="BF10" t="n">
         <v>0</v>
       </c>
+      <c r="BG10" t="n">
+        <v>730780</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -2483,6 +2515,9 @@
       <c r="BF11" t="n">
         <v>0</v>
       </c>
+      <c r="BG11" t="n">
+        <v>730625</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -2659,6 +2694,9 @@
       <c r="BF12" t="n">
         <v>0</v>
       </c>
+      <c r="BG12" t="n">
+        <v>725462</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -2835,6 +2873,9 @@
       <c r="BF13" t="n">
         <v>0</v>
       </c>
+      <c r="BG13" t="n">
+        <v>690758</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -3011,6 +3052,9 @@
       <c r="BF14" t="n">
         <v>0</v>
       </c>
+      <c r="BG14" t="n">
+        <v>726847</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -3187,6 +3231,9 @@
       <c r="BF15" t="n">
         <v>0</v>
       </c>
+      <c r="BG15" t="n">
+        <v>724021</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -3363,6 +3410,9 @@
       <c r="BF16" t="n">
         <v>0</v>
       </c>
+      <c r="BG16" t="n">
+        <v>750112</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -3539,6 +3589,9 @@
       <c r="BF17" t="n">
         <v>0</v>
       </c>
+      <c r="BG17" t="n">
+        <v>750236</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -3715,6 +3768,9 @@
       <c r="BF18" t="n">
         <v>0</v>
       </c>
+      <c r="BG18" t="n">
+        <v>711595</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -3891,6 +3947,9 @@
       <c r="BF19" t="n">
         <v>0</v>
       </c>
+      <c r="BG19" t="n">
+        <v>683245</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -4067,6 +4126,9 @@
       <c r="BF20" t="n">
         <v>0</v>
       </c>
+      <c r="BG20" t="n">
+        <v>652929</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -4243,6 +4305,9 @@
       <c r="BF21" t="n">
         <v>0</v>
       </c>
+      <c r="BG21" t="n">
+        <v>734689</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -4419,6 +4484,9 @@
       <c r="BF22" t="n">
         <v>0</v>
       </c>
+      <c r="BG22" t="n">
+        <v>722215</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -4595,6 +4663,9 @@
       <c r="BF23" t="n">
         <v>0</v>
       </c>
+      <c r="BG23" t="n">
+        <v>721558</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -4771,6 +4842,9 @@
       <c r="BF24" t="n">
         <v>0</v>
       </c>
+      <c r="BG24" t="n">
+        <v>715981</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -4947,6 +5021,9 @@
       <c r="BF25" t="n">
         <v>0</v>
       </c>
+      <c r="BG25" t="n">
+        <v>696196</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -5123,6 +5200,9 @@
       <c r="BF26" t="n">
         <v>0</v>
       </c>
+      <c r="BG26" t="n">
+        <v>676252</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -5299,6 +5379,9 @@
       <c r="BF27" t="n">
         <v>0</v>
       </c>
+      <c r="BG27" t="n">
+        <v>661253</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -5475,6 +5558,9 @@
       <c r="BF28" t="n">
         <v>0</v>
       </c>
+      <c r="BG28" t="n">
+        <v>725641</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -5651,6 +5737,9 @@
       <c r="BF29" t="n">
         <v>0</v>
       </c>
+      <c r="BG29" t="n">
+        <v>705659</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -5827,6 +5916,9 @@
       <c r="BF30" t="n">
         <v>0</v>
       </c>
+      <c r="BG30" t="n">
+        <v>697433</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -6003,6 +6095,9 @@
       <c r="BF31" t="n">
         <v>0</v>
       </c>
+      <c r="BG31" t="n">
+        <v>690315</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -6179,6 +6274,9 @@
       <c r="BF32" t="n">
         <v>0</v>
       </c>
+      <c r="BG32" t="n">
+        <v>663628</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -6355,6 +6453,9 @@
       <c r="BF33" t="n">
         <v>0</v>
       </c>
+      <c r="BG33" t="n">
+        <v>642547</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -6531,6 +6632,9 @@
       <c r="BF34" t="n">
         <v>0</v>
       </c>
+      <c r="BG34" t="n">
+        <v>635451</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -6707,6 +6811,9 @@
       <c r="BF35" t="n">
         <v>0</v>
       </c>
+      <c r="BG35" t="n">
+        <v>774137</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -6883,6 +6990,9 @@
       <c r="BF36" t="n">
         <v>0</v>
       </c>
+      <c r="BG36" t="n">
+        <v>750903</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -7059,6 +7169,9 @@
       <c r="BF37" t="n">
         <v>0</v>
       </c>
+      <c r="BG37" t="n">
+        <v>749469</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -7235,6 +7348,9 @@
       <c r="BF38" t="n">
         <v>0</v>
       </c>
+      <c r="BG38" t="n">
+        <v>745350</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -7411,6 +7527,9 @@
       <c r="BF39" t="n">
         <v>0</v>
       </c>
+      <c r="BG39" t="n">
+        <v>719109</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -7587,6 +7706,9 @@
       <c r="BF40" t="n">
         <v>0</v>
       </c>
+      <c r="BG40" t="n">
+        <v>692520</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -7763,6 +7885,9 @@
       <c r="BF41" t="n">
         <v>0</v>
       </c>
+      <c r="BG41" t="n">
+        <v>683638</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -7939,6 +8064,9 @@
       <c r="BF42" t="n">
         <v>0</v>
       </c>
+      <c r="BG42" t="n">
+        <v>776955</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -8115,6 +8243,9 @@
       <c r="BF43" t="n">
         <v>0</v>
       </c>
+      <c r="BG43" t="n">
+        <v>753184</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -8291,6 +8422,9 @@
       <c r="BF44" t="n">
         <v>0</v>
       </c>
+      <c r="BG44" t="n">
+        <v>783859</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -8467,6 +8601,9 @@
       <c r="BF45" t="n">
         <v>0</v>
       </c>
+      <c r="BG45" t="n">
+        <v>774023</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -8643,6 +8780,9 @@
       <c r="BF46" t="n">
         <v>0</v>
       </c>
+      <c r="BG46" t="n">
+        <v>729288</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -8819,6 +8959,9 @@
       <c r="BF47" t="n">
         <v>0</v>
       </c>
+      <c r="BG47" t="n">
+        <v>707917</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -8995,6 +9138,9 @@
       <c r="BF48" t="n">
         <v>0</v>
       </c>
+      <c r="BG48" t="n">
+        <v>701775</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -9171,6 +9317,9 @@
       <c r="BF49" t="n">
         <v>0</v>
       </c>
+      <c r="BG49" t="n">
+        <v>757683</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -9347,6 +9496,9 @@
       <c r="BF50" t="n">
         <v>0</v>
       </c>
+      <c r="BG50" t="n">
+        <v>747203</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -9523,6 +9675,9 @@
       <c r="BF51" t="n">
         <v>0</v>
       </c>
+      <c r="BG51" t="n">
+        <v>740290</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -9699,6 +9854,9 @@
       <c r="BF52" t="n">
         <v>0</v>
       </c>
+      <c r="BG52" t="n">
+        <v>740322</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -9875,6 +10033,9 @@
       <c r="BF53" t="n">
         <v>0</v>
       </c>
+      <c r="BG53" t="n">
+        <v>707743</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -10051,6 +10212,9 @@
       <c r="BF54" t="n">
         <v>0</v>
       </c>
+      <c r="BG54" t="n">
+        <v>670674</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -10227,6 +10391,9 @@
       <c r="BF55" t="n">
         <v>0</v>
       </c>
+      <c r="BG55" t="n">
+        <v>600421</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -10403,6 +10570,9 @@
       <c r="BF56" t="n">
         <v>0</v>
       </c>
+      <c r="BG56" t="n">
+        <v>715314</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -10579,6 +10749,9 @@
       <c r="BF57" t="n">
         <v>1</v>
       </c>
+      <c r="BG57" t="n">
+        <v>731599</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -10755,6 +10928,9 @@
       <c r="BF58" t="n">
         <v>0</v>
       </c>
+      <c r="BG58" t="n">
+        <v>724710</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -10931,6 +11107,9 @@
       <c r="BF59" t="n">
         <v>9</v>
       </c>
+      <c r="BG59" t="n">
+        <v>734845</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -11107,6 +11286,9 @@
       <c r="BF60" t="n">
         <v>6</v>
       </c>
+      <c r="BG60" t="n">
+        <v>711772</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -11283,6 +11465,9 @@
       <c r="BF61" t="n">
         <v>10</v>
       </c>
+      <c r="BG61" t="n">
+        <v>681688</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -11459,6 +11644,9 @@
       <c r="BF62" t="n">
         <v>5</v>
       </c>
+      <c r="BG62" t="n">
+        <v>673656</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
@@ -11635,6 +11823,9 @@
       <c r="BF63" t="n">
         <v>8</v>
       </c>
+      <c r="BG63" t="n">
+        <v>781217</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -11811,6 +12002,9 @@
       <c r="BF64" t="n">
         <v>3</v>
       </c>
+      <c r="BG64" t="n">
+        <v>754036</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -11987,6 +12181,9 @@
       <c r="BF65" t="n">
         <v>13</v>
       </c>
+      <c r="BG65" t="n">
+        <v>785573</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -12163,6 +12360,9 @@
       <c r="BF66" t="n">
         <v>12</v>
       </c>
+      <c r="BG66" t="n">
+        <v>778856</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
@@ -12339,6 +12539,9 @@
       <c r="BF67" t="n">
         <v>14</v>
       </c>
+      <c r="BG67" t="n">
+        <v>724534</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -12515,6 +12718,9 @@
       <c r="BF68" t="n">
         <v>4</v>
       </c>
+      <c r="BG68" t="n">
+        <v>557783</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
@@ -12691,6 +12897,9 @@
       <c r="BF69" t="n">
         <v>8</v>
       </c>
+      <c r="BG69" t="n">
+        <v>633176</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -12867,6 +13076,9 @@
       <c r="BF70" t="n">
         <v>7</v>
       </c>
+      <c r="BG70" t="n">
+        <v>798608</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
@@ -13043,6 +13255,9 @@
       <c r="BF71" t="n">
         <v>8</v>
       </c>
+      <c r="BG71" t="n">
+        <v>791343</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -13219,6 +13434,9 @@
       <c r="BF72" t="n">
         <v>19</v>
       </c>
+      <c r="BG72" t="n">
+        <v>790028</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
@@ -13395,6 +13613,9 @@
       <c r="BF73" t="n">
         <v>13</v>
       </c>
+      <c r="BG73" t="n">
+        <v>787789</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
@@ -13571,6 +13792,9 @@
       <c r="BF74" t="n">
         <v>12</v>
       </c>
+      <c r="BG74" t="n">
+        <v>764929</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
@@ -13747,6 +13971,9 @@
       <c r="BF75" t="n">
         <v>14</v>
       </c>
+      <c r="BG75" t="n">
+        <v>737765</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -13923,6 +14150,9 @@
       <c r="BF76" t="n">
         <v>7</v>
       </c>
+      <c r="BG76" t="n">
+        <v>731326</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
@@ -14099,6 +14329,9 @@
       <c r="BF77" t="n">
         <v>7</v>
       </c>
+      <c r="BG77" t="n">
+        <v>778111</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
@@ -14275,6 +14508,9 @@
       <c r="BF78" t="n">
         <v>10</v>
       </c>
+      <c r="BG78" t="n">
+        <v>786944</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
@@ -14451,6 +14687,9 @@
       <c r="BF79" t="n">
         <v>14</v>
       </c>
+      <c r="BG79" t="n">
+        <v>782416</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
@@ -14627,6 +14866,9 @@
       <c r="BF80" t="n">
         <v>15</v>
       </c>
+      <c r="BG80" t="n">
+        <v>801872</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
@@ -14803,6 +15045,9 @@
       <c r="BF81" t="n">
         <v>20</v>
       </c>
+      <c r="BG81" t="n">
+        <v>773310</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
@@ -14979,6 +15224,9 @@
       <c r="BF82" t="n">
         <v>12</v>
       </c>
+      <c r="BG82" t="n">
+        <v>737402</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
@@ -15155,6 +15403,9 @@
       <c r="BF83" t="n">
         <v>11</v>
       </c>
+      <c r="BG83" t="n">
+        <v>739397</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -15331,6 +15582,9 @@
       <c r="BF84" t="n">
         <v>14</v>
       </c>
+      <c r="BG84" t="n">
+        <v>803822</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
@@ -15507,6 +15761,9 @@
       <c r="BF85" t="n">
         <v>11</v>
       </c>
+      <c r="BG85" t="n">
+        <v>809792</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
@@ -15683,6 +15940,9 @@
       <c r="BF86" t="n">
         <v>12</v>
       </c>
+      <c r="BG86" t="n">
+        <v>807512</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
@@ -15859,6 +16119,9 @@
       <c r="BF87" t="n">
         <v>23</v>
       </c>
+      <c r="BG87" t="n">
+        <v>791619</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -16035,6 +16298,9 @@
       <c r="BF88" t="n">
         <v>26</v>
       </c>
+      <c r="BG88" t="n">
+        <v>761241</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
@@ -16211,6 +16477,9 @@
       <c r="BF89" t="n">
         <v>16</v>
       </c>
+      <c r="BG89" t="n">
+        <v>722556</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
@@ -16387,6 +16656,9 @@
       <c r="BF90" t="n">
         <v>17</v>
       </c>
+      <c r="BG90" t="n">
+        <v>712338</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
@@ -16563,6 +16835,9 @@
       <c r="BF91" t="n">
         <v>19</v>
       </c>
+      <c r="BG91" t="n">
+        <v>809263</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
@@ -16739,6 +17014,9 @@
       <c r="BF92" t="n">
         <v>16</v>
       </c>
+      <c r="BG92" t="n">
+        <v>812913</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
@@ -16915,6 +17193,9 @@
       <c r="BF93" t="n">
         <v>24</v>
       </c>
+      <c r="BG93" t="n">
+        <v>821283</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
@@ -17091,6 +17372,9 @@
       <c r="BF94" t="n">
         <v>25</v>
       </c>
+      <c r="BG94" t="n">
+        <v>838298</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
@@ -17267,6 +17551,9 @@
       <c r="BF95" t="n">
         <v>38</v>
       </c>
+      <c r="BG95" t="n">
+        <v>792958</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
@@ -17443,6 +17730,9 @@
       <c r="BF96" t="n">
         <v>21</v>
       </c>
+      <c r="BG96" t="n">
+        <v>750512</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
@@ -17619,6 +17909,9 @@
       <c r="BF97" t="n">
         <v>18</v>
       </c>
+      <c r="BG97" t="n">
+        <v>739629</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
@@ -17795,6 +18088,9 @@
       <c r="BF98" t="n">
         <v>29</v>
       </c>
+      <c r="BG98" t="n">
+        <v>809428</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
@@ -17971,6 +18267,9 @@
       <c r="BF99" t="n">
         <v>29</v>
       </c>
+      <c r="BG99" t="n">
+        <v>808646</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
@@ -18147,6 +18446,9 @@
       <c r="BF100" t="n">
         <v>24</v>
       </c>
+      <c r="BG100" t="n">
+        <v>806012</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
@@ -18323,6 +18625,9 @@
       <c r="BF101" t="n">
         <v>39</v>
       </c>
+      <c r="BG101" t="n">
+        <v>834899</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
@@ -18499,6 +18804,9 @@
       <c r="BF102" t="n">
         <v>30</v>
       </c>
+      <c r="BG102" t="n">
+        <v>824434</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
@@ -18675,6 +18983,9 @@
       <c r="BF103" t="n">
         <v>23</v>
       </c>
+      <c r="BG103" t="n">
+        <v>779875</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
@@ -18851,6 +19162,9 @@
       <c r="BF104" t="n">
         <v>31</v>
       </c>
+      <c r="BG104" t="n">
+        <v>763799</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
@@ -19027,6 +19341,9 @@
       <c r="BF105" t="n">
         <v>37</v>
       </c>
+      <c r="BG105" t="n">
+        <v>846481</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
@@ -19203,6 +19520,9 @@
       <c r="BF106" t="n">
         <v>40</v>
       </c>
+      <c r="BG106" t="n">
+        <v>846977</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
@@ -19379,6 +19699,9 @@
       <c r="BF107" t="n">
         <v>31</v>
       </c>
+      <c r="BG107" t="n">
+        <v>833933</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
@@ -19555,6 +19878,9 @@
       <c r="BF108" t="n">
         <v>34</v>
       </c>
+      <c r="BG108" t="n">
+        <v>808720</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
@@ -19731,6 +20057,9 @@
       <c r="BF109" t="n">
         <v>25</v>
       </c>
+      <c r="BG109" t="n">
+        <v>772459</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
@@ -19907,6 +20236,9 @@
       <c r="BF110" t="n">
         <v>28</v>
       </c>
+      <c r="BG110" t="n">
+        <v>674036</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
@@ -20083,6 +20415,9 @@
       <c r="BF111" t="n">
         <v>27</v>
       </c>
+      <c r="BG111" t="n">
+        <v>603635</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
@@ -20259,6 +20594,9 @@
       <c r="BF112" t="n">
         <v>46</v>
       </c>
+      <c r="BG112" t="n">
+        <v>818101</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
@@ -20435,6 +20773,9 @@
       <c r="BF113" t="n">
         <v>40</v>
       </c>
+      <c r="BG113" t="n">
+        <v>810673</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
@@ -20611,6 +20952,9 @@
       <c r="BF114" t="n">
         <v>36</v>
       </c>
+      <c r="BG114" t="n">
+        <v>809649</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
@@ -20787,6 +21131,9 @@
       <c r="BF115" t="n">
         <v>53</v>
       </c>
+      <c r="BG115" t="n">
+        <v>801119</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
@@ -20963,6 +21310,9 @@
       <c r="BF116" t="n">
         <v>61</v>
       </c>
+      <c r="BG116" t="n">
+        <v>780090</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
@@ -21139,6 +21489,9 @@
       <c r="BF117" t="n">
         <v>37</v>
       </c>
+      <c r="BG117" t="n">
+        <v>728326</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
@@ -21315,6 +21668,9 @@
       <c r="BF118" t="n">
         <v>42</v>
       </c>
+      <c r="BG118" t="n">
+        <v>740301</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
@@ -21491,6 +21847,9 @@
       <c r="BF119" t="n">
         <v>53</v>
       </c>
+      <c r="BG119" t="n">
+        <v>798389</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
@@ -21667,6 +22026,9 @@
       <c r="BF120" t="n">
         <v>56</v>
       </c>
+      <c r="BG120" t="n">
+        <v>790997</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
@@ -21843,6 +22205,9 @@
       <c r="BF121" t="n">
         <v>59</v>
       </c>
+      <c r="BG121" t="n">
+        <v>765634</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
@@ -22019,6 +22384,9 @@
       <c r="BF122" t="n">
         <v>60</v>
       </c>
+      <c r="BG122" t="n">
+        <v>662574</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
@@ -22195,6 +22563,9 @@
       <c r="BF123" t="n">
         <v>56</v>
       </c>
+      <c r="BG123" t="n">
+        <v>693051</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
@@ -22371,6 +22742,9 @@
       <c r="BF124" t="n">
         <v>43</v>
       </c>
+      <c r="BG124" t="n">
+        <v>702040</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
@@ -22547,6 +22921,9 @@
       <c r="BF125" t="n">
         <v>43</v>
       </c>
+      <c r="BG125" t="n">
+        <v>716408</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
@@ -22723,6 +23100,9 @@
       <c r="BF126" t="n">
         <v>41</v>
       </c>
+      <c r="BG126" t="n">
+        <v>826515</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
@@ -22899,6 +23279,9 @@
       <c r="BF127" t="n">
         <v>58</v>
       </c>
+      <c r="BG127" t="n">
+        <v>808540</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
@@ -23075,6 +23458,9 @@
       <c r="BF128" t="n">
         <v>41</v>
       </c>
+      <c r="BG128" t="n">
+        <v>769011</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
@@ -23251,6 +23637,9 @@
       <c r="BF129" t="n">
         <v>46</v>
       </c>
+      <c r="BG129" t="n">
+        <v>692298</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
@@ -23427,6 +23816,9 @@
       <c r="BF130" t="n">
         <v>34</v>
       </c>
+      <c r="BG130" t="n">
+        <v>477916</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
@@ -23603,6 +23995,9 @@
       <c r="BF131" t="n">
         <v>40</v>
       </c>
+      <c r="BG131" t="n">
+        <v>652017</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
@@ -23779,6 +24174,9 @@
       <c r="BF132" t="n">
         <v>26</v>
       </c>
+      <c r="BG132" t="n">
+        <v>719120</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
@@ -23955,6 +24353,9 @@
       <c r="BF133" t="n">
         <v>41</v>
       </c>
+      <c r="BG133" t="n">
+        <v>839314</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
@@ -24131,6 +24532,9 @@
       <c r="BF134" t="n">
         <v>48</v>
       </c>
+      <c r="BG134" t="n">
+        <v>808489</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
@@ -24307,6 +24711,9 @@
       <c r="BF135" t="n">
         <v>56</v>
       </c>
+      <c r="BG135" t="n">
+        <v>819718</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
@@ -24483,6 +24890,9 @@
       <c r="BF136" t="n">
         <v>57</v>
       </c>
+      <c r="BG136" t="n">
+        <v>818388</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
@@ -24659,6 +25069,9 @@
       <c r="BF137" t="n">
         <v>50</v>
       </c>
+      <c r="BG137" t="n">
+        <v>768201</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
@@ -24835,6 +25248,9 @@
       <c r="BF138" t="n">
         <v>37</v>
       </c>
+      <c r="BG138" t="n">
+        <v>688972</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
@@ -25011,6 +25427,9 @@
       <c r="BF139" t="n">
         <v>53</v>
       </c>
+      <c r="BG139" t="n">
+        <v>700110</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
@@ -25187,6 +25606,9 @@
       <c r="BF140" t="n">
         <v>56</v>
       </c>
+      <c r="BG140" t="n">
+        <v>818039</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
@@ -25363,6 +25785,9 @@
       <c r="BF141" t="n">
         <v>52</v>
       </c>
+      <c r="BG141" t="n">
+        <v>812126</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
@@ -25539,6 +25964,9 @@
       <c r="BF142" t="n">
         <v>63</v>
       </c>
+      <c r="BG142" t="n">
+        <v>784182</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
@@ -25715,6 +26143,9 @@
       <c r="BF143" t="n">
         <v>64</v>
       </c>
+      <c r="BG143" t="n">
+        <v>764288</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
@@ -25891,6 +26322,9 @@
       <c r="BF144" t="n">
         <v>57</v>
       </c>
+      <c r="BG144" t="n">
+        <v>728386</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
@@ -26067,6 +26501,9 @@
       <c r="BF145" t="n">
         <v>45</v>
       </c>
+      <c r="BG145" t="n">
+        <v>572786</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
@@ -26243,6 +26680,9 @@
       <c r="BF146" t="n">
         <v>66</v>
       </c>
+      <c r="BG146" t="n">
+        <v>648910</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
@@ -26419,6 +26859,9 @@
       <c r="BF147" t="n">
         <v>68</v>
       </c>
+      <c r="BG147" t="n">
+        <v>757744</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
@@ -26595,6 +27038,9 @@
       <c r="BF148" t="n">
         <v>78</v>
       </c>
+      <c r="BG148" t="n">
+        <v>755587</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
@@ -26771,6 +27217,9 @@
       <c r="BF149" t="n">
         <v>77</v>
       </c>
+      <c r="BG149" t="n">
+        <v>748008</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
@@ -26947,6 +27396,9 @@
       <c r="BF150" t="n">
         <v>83</v>
       </c>
+      <c r="BG150" t="n">
+        <v>700952</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
@@ -27123,6 +27575,9 @@
       <c r="BF151" t="n">
         <v>87</v>
       </c>
+      <c r="BG151" t="n">
+        <v>662973</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
@@ -27299,6 +27754,9 @@
       <c r="BF152" t="n">
         <v>54</v>
       </c>
+      <c r="BG152" t="n">
+        <v>603458</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
@@ -27475,6 +27933,9 @@
       <c r="BF153" t="n">
         <v>58</v>
       </c>
+      <c r="BG153" t="n">
+        <v>582445</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
@@ -27651,6 +28112,9 @@
       <c r="BF154" t="n">
         <v>90</v>
       </c>
+      <c r="BG154" t="n">
+        <v>709565</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
@@ -27827,6 +28291,9 @@
       <c r="BF155" t="n">
         <v>82</v>
       </c>
+      <c r="BG155" t="n">
+        <v>736859</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
@@ -28003,6 +28470,9 @@
       <c r="BF156" t="n">
         <v>84</v>
       </c>
+      <c r="BG156" t="n">
+        <v>727345</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
@@ -28179,6 +28649,9 @@
       <c r="BF157" t="n">
         <v>72</v>
       </c>
+      <c r="BG157" t="n">
+        <v>724667</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
@@ -28355,6 +28828,9 @@
       <c r="BF158" t="n">
         <v>58</v>
       </c>
+      <c r="BG158" t="n">
+        <v>667010</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
@@ -28531,6 +29007,9 @@
       <c r="BF159" t="n">
         <v>52</v>
       </c>
+      <c r="BG159" t="n">
+        <v>600224</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
@@ -28707,6 +29186,9 @@
       <c r="BF160" t="n">
         <v>62</v>
       </c>
+      <c r="BG160" t="n">
+        <v>605284</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
@@ -28883,6 +29365,9 @@
       <c r="BF161" t="n">
         <v>62</v>
       </c>
+      <c r="BG161" t="n">
+        <v>716371</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
@@ -29059,6 +29544,9 @@
       <c r="BF162" t="n">
         <v>71</v>
       </c>
+      <c r="BG162" t="n">
+        <v>734500</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
@@ -29235,6 +29723,9 @@
       <c r="BF163" t="n">
         <v>88</v>
       </c>
+      <c r="BG163" t="n">
+        <v>735184</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
@@ -29411,6 +29902,9 @@
       <c r="BF164" t="n">
         <v>65</v>
       </c>
+      <c r="BG164" t="n">
+        <v>624796</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
@@ -29587,6 +30081,9 @@
       <c r="BF165" t="n">
         <v>49</v>
       </c>
+      <c r="BG165" t="n">
+        <v>622097</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
@@ -29763,6 +30260,9 @@
       <c r="BF166" t="n">
         <v>46</v>
       </c>
+      <c r="BG166" t="n">
+        <v>594370</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
@@ -29939,6 +30439,9 @@
       <c r="BF167" t="n">
         <v>58</v>
       </c>
+      <c r="BG167" t="n">
+        <v>612857</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
@@ -30115,6 +30618,9 @@
       <c r="BF168" t="n">
         <v>73</v>
       </c>
+      <c r="BG168" t="n">
+        <v>724285</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
@@ -30291,6 +30797,9 @@
       <c r="BF169" t="n">
         <v>67</v>
       </c>
+      <c r="BG169" t="n">
+        <v>704251</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
@@ -30467,6 +30976,9 @@
       <c r="BF170" t="n">
         <v>69</v>
       </c>
+      <c r="BG170" t="n">
+        <v>709962</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
@@ -30643,6 +31155,9 @@
       <c r="BF171" t="n">
         <v>69</v>
       </c>
+      <c r="BG171" t="n">
+        <v>695047</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
@@ -30819,6 +31334,9 @@
       <c r="BF172" t="n">
         <v>57</v>
       </c>
+      <c r="BG172" t="n">
+        <v>672796</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
@@ -30995,6 +31513,9 @@
       <c r="BF173" t="n">
         <v>49</v>
       </c>
+      <c r="BG173" t="n">
+        <v>624700</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
@@ -31171,6 +31692,9 @@
       <c r="BF174" t="n">
         <v>58</v>
       </c>
+      <c r="BG174" t="n">
+        <v>613653</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
@@ -31347,6 +31871,9 @@
       <c r="BF175" t="n">
         <v>43</v>
       </c>
+      <c r="BG175" t="n">
+        <v>704223</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
@@ -31523,6 +32050,9 @@
       <c r="BF176" t="n">
         <v>48</v>
       </c>
+      <c r="BG176" t="n">
+        <v>669405</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
@@ -31699,6 +32229,9 @@
       <c r="BF177" t="n">
         <v>65</v>
       </c>
+      <c r="BG177" t="n">
+        <v>692360</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
@@ -31875,6 +32408,9 @@
       <c r="BF178" t="n">
         <v>92</v>
       </c>
+      <c r="BG178" t="n">
+        <v>704874</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
@@ -32051,6 +32587,9 @@
       <c r="BF179" t="n">
         <v>76</v>
       </c>
+      <c r="BG179" t="n">
+        <v>640435</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
@@ -32227,6 +32766,9 @@
       <c r="BF180" t="n">
         <v>70</v>
       </c>
+      <c r="BG180" t="n">
+        <v>586902</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
@@ -32403,6 +32945,9 @@
       <c r="BF181" t="n">
         <v>78</v>
       </c>
+      <c r="BG181" t="n">
+        <v>594929</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
@@ -32579,6 +33124,9 @@
       <c r="BF182" t="n">
         <v>90</v>
       </c>
+      <c r="BG182" t="n">
+        <v>702671</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
@@ -32755,6 +33303,9 @@
       <c r="BF183" t="n">
         <v>101</v>
       </c>
+      <c r="BG183" t="n">
+        <v>698908</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
@@ -32931,6 +33482,9 @@
       <c r="BF184" t="n">
         <v>111</v>
       </c>
+      <c r="BG184" t="n">
+        <v>703480</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
@@ -33107,6 +33661,9 @@
       <c r="BF185" t="n">
         <v>81</v>
       </c>
+      <c r="BG185" t="n">
+        <v>695554</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
@@ -33283,6 +33840,9 @@
       <c r="BF186" t="n">
         <v>104</v>
       </c>
+      <c r="BG186" t="n">
+        <v>649638</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
@@ -33459,6 +34019,9 @@
       <c r="BF187" t="n">
         <v>86</v>
       </c>
+      <c r="BG187" t="n">
+        <v>571297</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
@@ -33635,6 +34198,9 @@
       <c r="BF188" t="n">
         <v>97</v>
       </c>
+      <c r="BG188" t="n">
+        <v>580160</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
@@ -33811,6 +34377,9 @@
       <c r="BF189" t="n">
         <v>100</v>
       </c>
+      <c r="BG189" t="n">
+        <v>695513</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
@@ -33987,6 +34556,9 @@
       <c r="BF190" t="n">
         <v>109</v>
       </c>
+      <c r="BG190" t="n">
+        <v>679292</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
@@ -34163,6 +34735,9 @@
       <c r="BF191" t="n">
         <v>101</v>
       </c>
+      <c r="BG191" t="n">
+        <v>681019</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
@@ -34339,6 +34914,9 @@
       <c r="BF192" t="n">
         <v>105</v>
       </c>
+      <c r="BG192" t="n">
+        <v>677185</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
@@ -34515,6 +35093,9 @@
       <c r="BF193" t="n">
         <v>92</v>
       </c>
+      <c r="BG193" t="n">
+        <v>648141</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
@@ -34691,6 +35272,9 @@
       <c r="BF194" t="n">
         <v>105</v>
       </c>
+      <c r="BG194" t="n">
+        <v>573749</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
@@ -34867,6 +35451,9 @@
       <c r="BF195" t="n">
         <v>87</v>
       </c>
+      <c r="BG195" t="n">
+        <v>577977</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
@@ -35043,6 +35630,9 @@
       <c r="BF196" t="n">
         <v>98</v>
       </c>
+      <c r="BG196" t="n">
+        <v>696257</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
@@ -35219,6 +35809,9 @@
       <c r="BF197" t="n">
         <v>81</v>
       </c>
+      <c r="BG197" t="n">
+        <v>694946</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
@@ -35395,6 +35988,9 @@
       <c r="BF198" t="n">
         <v>118</v>
       </c>
+      <c r="BG198" t="n">
+        <v>692282</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
@@ -35571,6 +36167,9 @@
       <c r="BF199" t="n">
         <v>119</v>
       </c>
+      <c r="BG199" t="n">
+        <v>680413</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
@@ -35747,6 +36346,9 @@
       <c r="BF200" t="n">
         <v>103</v>
       </c>
+      <c r="BG200" t="n">
+        <v>644514</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
@@ -35923,6 +36525,9 @@
       <c r="BF201" t="n">
         <v>91</v>
       </c>
+      <c r="BG201" t="n">
+        <v>572128</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
@@ -36099,6 +36704,9 @@
       <c r="BF202" t="n">
         <v>95</v>
       </c>
+      <c r="BG202" t="n">
+        <v>573642</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
@@ -36275,6 +36883,9 @@
       <c r="BF203" t="n">
         <v>109</v>
       </c>
+      <c r="BG203" t="n">
+        <v>683506</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
@@ -36451,6 +37062,9 @@
       <c r="BF204" t="n">
         <v>132</v>
       </c>
+      <c r="BG204" t="n">
+        <v>682613</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
@@ -36627,6 +37241,9 @@
       <c r="BF205" t="n">
         <v>126</v>
       </c>
+      <c r="BG205" t="n">
+        <v>675838</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
@@ -36803,6 +37420,9 @@
       <c r="BF206" t="n">
         <v>138</v>
       </c>
+      <c r="BG206" t="n">
+        <v>667251</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
@@ -36979,6 +37599,9 @@
       <c r="BF207" t="n">
         <v>139</v>
       </c>
+      <c r="BG207" t="n">
+        <v>613739</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
@@ -37155,6 +37778,9 @@
       <c r="BF208" t="n">
         <v>133</v>
       </c>
+      <c r="BG208" t="n">
+        <v>546361</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
@@ -37331,6 +37957,9 @@
       <c r="BF209" t="n">
         <v>126</v>
       </c>
+      <c r="BG209" t="n">
+        <v>548747</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
@@ -37507,6 +38136,9 @@
       <c r="BF210" t="n">
         <v>152</v>
       </c>
+      <c r="BG210" t="n">
+        <v>672046</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
@@ -37683,6 +38315,9 @@
       <c r="BF211" t="n">
         <v>103</v>
       </c>
+      <c r="BG211" t="n">
+        <v>664254</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
@@ -37859,6 +38494,9 @@
       <c r="BF212" t="n">
         <v>139</v>
       </c>
+      <c r="BG212" t="n">
+        <v>660070</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
@@ -38035,6 +38673,9 @@
       <c r="BF213" t="n">
         <v>166</v>
       </c>
+      <c r="BG213" t="n">
+        <v>652150</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
@@ -38211,6 +38852,9 @@
       <c r="BF214" t="n">
         <v>149</v>
       </c>
+      <c r="BG214" t="n">
+        <v>636523</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
@@ -38387,6 +39031,9 @@
       <c r="BF215" t="n">
         <v>125</v>
       </c>
+      <c r="BG215" t="n">
+        <v>570187</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
@@ -38563,6 +39210,9 @@
       <c r="BF216" t="n">
         <v>112</v>
       </c>
+      <c r="BG216" t="n">
+        <v>567103</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
@@ -38739,6 +39389,9 @@
       <c r="BF217" t="n">
         <v>138</v>
       </c>
+      <c r="BG217" t="n">
+        <v>681698</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
@@ -38915,6 +39568,9 @@
       <c r="BF218" t="n">
         <v>163</v>
       </c>
+      <c r="BG218" t="n">
+        <v>695653</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
@@ -39091,6 +39747,9 @@
       <c r="BF219" t="n">
         <v>189</v>
       </c>
+      <c r="BG219" t="n">
+        <v>692204</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
@@ -39267,6 +39926,9 @@
       <c r="BF220" t="n">
         <v>200</v>
       </c>
+      <c r="BG220" t="n">
+        <v>691003</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
@@ -39443,6 +40105,9 @@
       <c r="BF221" t="n">
         <v>198</v>
       </c>
+      <c r="BG221" t="n">
+        <v>654102</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
@@ -39619,6 +40284,9 @@
       <c r="BF222" t="n">
         <v>173</v>
       </c>
+      <c r="BG222" t="n">
+        <v>595106</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
@@ -39795,6 +40463,9 @@
       <c r="BF223" t="n">
         <v>190</v>
       </c>
+      <c r="BG223" t="n">
+        <v>608079</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
@@ -39971,6 +40642,9 @@
       <c r="BF224" t="n">
         <v>201</v>
       </c>
+      <c r="BG224" t="n">
+        <v>721931</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
@@ -40147,6 +40821,9 @@
       <c r="BF225" t="n">
         <v>207</v>
       </c>
+      <c r="BG225" t="n">
+        <v>735706</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
@@ -40323,6 +41000,9 @@
       <c r="BF226" t="n">
         <v>250</v>
       </c>
+      <c r="BG226" t="n">
+        <v>732835</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
@@ -40499,6 +41179,9 @@
       <c r="BF227" t="n">
         <v>207</v>
       </c>
+      <c r="BG227" t="n">
+        <v>717941</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
@@ -40675,6 +41358,9 @@
       <c r="BF228" t="n">
         <v>232</v>
       </c>
+      <c r="BG228" t="n">
+        <v>693157</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
@@ -40851,6 +41537,9 @@
       <c r="BF229" t="n">
         <v>202</v>
       </c>
+      <c r="BG229" t="n">
+        <v>628785</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
@@ -41027,6 +41716,9 @@
       <c r="BF230" t="n">
         <v>187</v>
       </c>
+      <c r="BG230" t="n">
+        <v>632815</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
@@ -41203,6 +41895,9 @@
       <c r="BF231" t="n">
         <v>240</v>
       </c>
+      <c r="BG231" t="n">
+        <v>733895</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
@@ -41379,6 +42074,9 @@
       <c r="BF232" t="n">
         <v>196</v>
       </c>
+      <c r="BG232" t="n">
+        <v>746319</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
@@ -41555,6 +42253,9 @@
       <c r="BF233" t="n">
         <v>237</v>
       </c>
+      <c r="BG233" t="n">
+        <v>764955</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
@@ -41731,6 +42432,9 @@
       <c r="BF234" t="n">
         <v>245</v>
       </c>
+      <c r="BG234" t="n">
+        <v>763554</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
@@ -41907,6 +42611,9 @@
       <c r="BF235" t="n">
         <v>214</v>
       </c>
+      <c r="BG235" t="n">
+        <v>721309</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
@@ -42083,6 +42790,9 @@
       <c r="BF236" t="n">
         <v>163</v>
       </c>
+      <c r="BG236" t="n">
+        <v>666732</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
@@ -42259,6 +42969,9 @@
       <c r="BF237" t="n">
         <v>159</v>
       </c>
+      <c r="BG237" t="n">
+        <v>674680</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
@@ -42435,6 +43148,9 @@
       <c r="BF238" t="n">
         <v>190</v>
       </c>
+      <c r="BG238" t="n">
+        <v>785542</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
@@ -42611,6 +43327,9 @@
       <c r="BF239" t="n">
         <v>192</v>
       </c>
+      <c r="BG239" t="n">
+        <v>787761</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
@@ -42787,6 +43506,9 @@
       <c r="BF240" t="n">
         <v>208</v>
       </c>
+      <c r="BG240" t="n">
+        <v>781430</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
@@ -42963,6 +43685,9 @@
       <c r="BF241" t="n">
         <v>218</v>
       </c>
+      <c r="BG241" t="n">
+        <v>767736</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
@@ -43139,6 +43864,9 @@
       <c r="BF242" t="n">
         <v>238</v>
       </c>
+      <c r="BG242" t="n">
+        <v>744012</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
@@ -43315,6 +44043,9 @@
       <c r="BF243" t="n">
         <v>200</v>
       </c>
+      <c r="BG243" t="n">
+        <v>671767</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
@@ -43491,6 +44222,9 @@
       <c r="BF244" t="n">
         <v>192</v>
       </c>
+      <c r="BG244" t="n">
+        <v>652196</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
@@ -43667,6 +44401,9 @@
       <c r="BF245" t="n">
         <v>215</v>
       </c>
+      <c r="BG245" t="n">
+        <v>687233</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
@@ -43843,6 +44580,9 @@
       <c r="BF246" t="n">
         <v>258</v>
       </c>
+      <c r="BG246" t="n">
+        <v>737180</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
@@ -44019,6 +44759,9 @@
       <c r="BF247" t="n">
         <v>245</v>
       </c>
+      <c r="BG247" t="n">
+        <v>761214</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
@@ -44195,6 +44938,9 @@
       <c r="BF248" t="n">
         <v>306</v>
       </c>
+      <c r="BG248" t="n">
+        <v>764074</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
@@ -44371,6 +45117,9 @@
       <c r="BF249" t="n">
         <v>309</v>
       </c>
+      <c r="BG249" t="n">
+        <v>727822</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
@@ -44547,6 +45296,9 @@
       <c r="BF250" t="n">
         <v>242</v>
       </c>
+      <c r="BG250" t="n">
+        <v>657008</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
@@ -44723,6 +45475,9 @@
       <c r="BF251" t="n">
         <v>249</v>
       </c>
+      <c r="BG251" t="n">
+        <v>644195</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n">
@@ -44899,6 +45654,9 @@
       <c r="BF252" t="n">
         <v>279</v>
       </c>
+      <c r="BG252" t="n">
+        <v>727441</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="n">
@@ -45075,6 +45833,9 @@
       <c r="BF253" t="n">
         <v>280</v>
       </c>
+      <c r="BG253" t="n">
+        <v>731067</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="n">
@@ -45251,6 +46012,9 @@
       <c r="BF254" t="n">
         <v>291</v>
       </c>
+      <c r="BG254" t="n">
+        <v>746862</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="n">
@@ -45427,6 +46191,9 @@
       <c r="BF255" t="n">
         <v>308</v>
       </c>
+      <c r="BG255" t="n">
+        <v>759649</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n">
@@ -45603,6 +46370,9 @@
       <c r="BF256" t="n">
         <v>315</v>
       </c>
+      <c r="BG256" t="n">
+        <v>722651</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="n">
@@ -45779,6 +46549,9 @@
       <c r="BF257" t="n">
         <v>270</v>
       </c>
+      <c r="BG257" t="n">
+        <v>667414</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n">
@@ -45955,6 +46728,9 @@
       <c r="BF258" t="n">
         <v>267</v>
       </c>
+      <c r="BG258" t="n">
+        <v>659614</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="n">
@@ -46131,6 +46907,9 @@
       <c r="BF259" t="n">
         <v>320</v>
       </c>
+      <c r="BG259" t="n">
+        <v>756905</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="n">
@@ -46307,6 +47086,9 @@
       <c r="BF260" t="n">
         <v>345</v>
       </c>
+      <c r="BG260" t="n">
+        <v>743577</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="n">
@@ -46483,6 +47265,9 @@
       <c r="BF261" t="n">
         <v>361</v>
       </c>
+      <c r="BG261" t="n">
+        <v>739917</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="n">
@@ -46659,6 +47444,9 @@
       <c r="BF262" t="n">
         <v>425</v>
       </c>
+      <c r="BG262" t="n">
+        <v>735689</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="n">
@@ -46835,6 +47623,9 @@
       <c r="BF263" t="n">
         <v>401</v>
       </c>
+      <c r="BG263" t="n">
+        <v>713010</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="n">
@@ -47011,6 +47802,9 @@
       <c r="BF264" t="n">
         <v>373</v>
       </c>
+      <c r="BG264" t="n">
+        <v>666111</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="n">
@@ -47187,6 +47981,9 @@
       <c r="BF265" t="n">
         <v>370</v>
       </c>
+      <c r="BG265" t="n">
+        <v>658371</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="n">
@@ -47363,6 +48160,9 @@
       <c r="BF266" t="n">
         <v>417</v>
       </c>
+      <c r="BG266" t="n">
+        <v>737098</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="n">
@@ -47539,6 +48339,9 @@
       <c r="BF267" t="n">
         <v>443</v>
       </c>
+      <c r="BG267" t="n">
+        <v>731139</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="n">
@@ -47715,6 +48518,9 @@
       <c r="BF268" t="n">
         <v>423</v>
       </c>
+      <c r="BG268" t="n">
+        <v>737486</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="n">
@@ -47891,6 +48697,9 @@
       <c r="BF269" t="n">
         <v>453</v>
       </c>
+      <c r="BG269" t="n">
+        <v>770774</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="n">
@@ -48067,6 +48876,9 @@
       <c r="BF270" t="n">
         <v>481</v>
       </c>
+      <c r="BG270" t="n">
+        <v>738317</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="n">
@@ -48243,6 +49055,9 @@
       <c r="BF271" t="n">
         <v>424</v>
       </c>
+      <c r="BG271" t="n">
+        <v>690062</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="n">
@@ -48419,6 +49234,9 @@
       <c r="BF272" t="n">
         <v>410</v>
       </c>
+      <c r="BG272" t="n">
+        <v>697477</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="n">
@@ -48595,6 +49413,9 @@
       <c r="BF273" t="n">
         <v>505</v>
       </c>
+      <c r="BG273" t="n">
+        <v>780841</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n">
@@ -48771,6 +49592,9 @@
       <c r="BF274" t="n">
         <v>529</v>
       </c>
+      <c r="BG274" t="n">
+        <v>776896</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="n">
@@ -48947,6 +49771,9 @@
       <c r="BF275" t="n">
         <v>513</v>
       </c>
+      <c r="BG275" t="n">
+        <v>766212</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="n">
@@ -49123,6 +49950,9 @@
       <c r="BF276" t="n">
         <v>492</v>
       </c>
+      <c r="BG276" t="n">
+        <v>763205</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="n">
@@ -49299,6 +50129,9 @@
       <c r="BF277" t="n">
         <v>490</v>
       </c>
+      <c r="BG277" t="n">
+        <v>746313</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="n">
@@ -49475,6 +50308,9 @@
       <c r="BF278" t="n">
         <v>437</v>
       </c>
+      <c r="BG278" t="n">
+        <v>699713</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="n">
@@ -49651,6 +50487,9 @@
       <c r="BF279" t="n">
         <v>439</v>
       </c>
+      <c r="BG279" t="n">
+        <v>701656</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="n">
@@ -49827,6 +50666,9 @@
       <c r="BF280" t="n">
         <v>519</v>
       </c>
+      <c r="BG280" t="n">
+        <v>774470</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="n">
@@ -50003,6 +50845,9 @@
       <c r="BF281" t="n">
         <v>575</v>
       </c>
+      <c r="BG281" t="n">
+        <v>756782</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="n">
@@ -50179,6 +51024,9 @@
       <c r="BF282" t="n">
         <v>472</v>
       </c>
+      <c r="BG282" t="n">
+        <v>748206</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="n">
@@ -50355,6 +51203,9 @@
       <c r="BF283" t="n">
         <v>622</v>
       </c>
+      <c r="BG283" t="n">
+        <v>746747</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="n">
@@ -50531,6 +51382,9 @@
       <c r="BF284" t="n">
         <v>546</v>
       </c>
+      <c r="BG284" t="n">
+        <v>758904</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="n">
@@ -50707,6 +51561,9 @@
       <c r="BF285" t="n">
         <v>442</v>
       </c>
+      <c r="BG285" t="n">
+        <v>717299</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="n">
@@ -50883,6 +51740,9 @@
       <c r="BF286" t="n">
         <v>476</v>
       </c>
+      <c r="BG286" t="n">
+        <v>730332</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="n">
@@ -51059,6 +51919,9 @@
       <c r="BF287" t="n">
         <v>563</v>
       </c>
+      <c r="BG287" t="n">
+        <v>810781</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="n">
@@ -51235,6 +52098,9 @@
       <c r="BF288" t="n">
         <v>604</v>
       </c>
+      <c r="BG288" t="n">
+        <v>808852</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="n">
@@ -51411,6 +52277,9 @@
       <c r="BF289" t="n">
         <v>582</v>
       </c>
+      <c r="BG289" t="n">
+        <v>803270</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="n">
@@ -51587,6 +52456,9 @@
       <c r="BF290" t="n">
         <v>639</v>
       </c>
+      <c r="BG290" t="n">
+        <v>786981</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="n">
@@ -51763,6 +52635,9 @@
       <c r="BF291" t="n">
         <v>674</v>
       </c>
+      <c r="BG291" t="n">
+        <v>743571</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="n">
@@ -51939,6 +52814,9 @@
       <c r="BF292" t="n">
         <v>542</v>
       </c>
+      <c r="BG292" t="n">
+        <v>703444</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="n">
@@ -52115,6 +52993,9 @@
       <c r="BF293" t="n">
         <v>466</v>
       </c>
+      <c r="BG293" t="n">
+        <v>696776</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="n">
@@ -52291,6 +53172,9 @@
       <c r="BF294" t="n">
         <v>566</v>
       </c>
+      <c r="BG294" t="n">
+        <v>774041</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="n">
@@ -52467,6 +53351,9 @@
       <c r="BF295" t="n">
         <v>646</v>
       </c>
+      <c r="BG295" t="n">
+        <v>758495</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="n">
@@ -52643,6 +53530,9 @@
       <c r="BF296" t="n">
         <v>616</v>
       </c>
+      <c r="BG296" t="n">
+        <v>748473</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="n">
@@ -52819,6 +53709,9 @@
       <c r="BF297" t="n">
         <v>690</v>
       </c>
+      <c r="BG297" t="n">
+        <v>737132</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="n">
@@ -52995,6 +53888,9 @@
       <c r="BF298" t="n">
         <v>644</v>
       </c>
+      <c r="BG298" t="n">
+        <v>749436</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="n">
@@ -53171,6 +54067,9 @@
       <c r="BF299" t="n">
         <v>546</v>
       </c>
+      <c r="BG299" t="n">
+        <v>677205</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="n">
@@ -53347,6 +54246,9 @@
       <c r="BF300" t="n">
         <v>550</v>
       </c>
+      <c r="BG300" t="n">
+        <v>665672</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="n">
@@ -53523,6 +54425,9 @@
       <c r="BF301" t="n">
         <v>679</v>
       </c>
+      <c r="BG301" t="n">
+        <v>717705</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="n">
@@ -53699,6 +54604,9 @@
       <c r="BF302" t="n">
         <v>675</v>
       </c>
+      <c r="BG302" t="n">
+        <v>728434</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="n">
@@ -53875,6 +54783,9 @@
       <c r="BF303" t="n">
         <v>648</v>
       </c>
+      <c r="BG303" t="n">
+        <v>718879</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="n">
@@ -54051,6 +54962,9 @@
       <c r="BF304" t="n">
         <v>741</v>
       </c>
+      <c r="BG304" t="n">
+        <v>703195</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="n">
@@ -54227,6 +55141,9 @@
       <c r="BF305" t="n">
         <v>685</v>
       </c>
+      <c r="BG305" t="n">
+        <v>763272</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="n">
@@ -54403,6 +55320,9 @@
       <c r="BF306" t="n">
         <v>692</v>
       </c>
+      <c r="BG306" t="n">
+        <v>679996</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="n">
@@ -54579,6 +55499,9 @@
       <c r="BF307" t="n">
         <v>655</v>
       </c>
+      <c r="BG307" t="n">
+        <v>663339</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="n">
@@ -54755,6 +55678,9 @@
       <c r="BF308" t="n">
         <v>694</v>
       </c>
+      <c r="BG308" t="n">
+        <v>708158</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="n">
@@ -54931,6 +55857,9 @@
       <c r="BF309" t="n">
         <v>693</v>
       </c>
+      <c r="BG309" t="n">
+        <v>716195</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="n">
@@ -55107,6 +56036,9 @@
       <c r="BF310" t="n">
         <v>731</v>
       </c>
+      <c r="BG310" t="n">
+        <v>746739</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="n">
@@ -55283,6 +56215,9 @@
       <c r="BF311" t="n">
         <v>784</v>
       </c>
+      <c r="BG311" t="n">
+        <v>757238</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="n">
@@ -55459,6 +56394,9 @@
       <c r="BF312" t="n">
         <v>865</v>
       </c>
+      <c r="BG312" t="n">
+        <v>854597</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="n">
@@ -55635,6 +56573,9 @@
       <c r="BF313" t="n">
         <v>596</v>
       </c>
+      <c r="BG313" t="n">
+        <v>732530</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="n">
@@ -55811,6 +56752,9 @@
       <c r="BF314" t="n">
         <v>611</v>
       </c>
+      <c r="BG314" t="n">
+        <v>728056</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="n">
@@ -55987,6 +56931,9 @@
       <c r="BF315" t="n">
         <v>767</v>
       </c>
+      <c r="BG315" t="n">
+        <v>811292</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="n">
@@ -56163,6 +57110,9 @@
       <c r="BF316" t="n">
         <v>767</v>
       </c>
+      <c r="BG316" t="n">
+        <v>794678</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="n">
@@ -56339,6 +57289,9 @@
       <c r="BF317" t="n">
         <v>819</v>
       </c>
+      <c r="BG317" t="n">
+        <v>814509</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="n">
@@ -56515,6 +57468,9 @@
       <c r="BF318" t="n">
         <v>826</v>
       </c>
+      <c r="BG318" t="n">
+        <v>812597</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="n">
@@ -56691,6 +57647,9 @@
       <c r="BF319" t="n">
         <v>915</v>
       </c>
+      <c r="BG319" t="n">
+        <v>779037</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="n">
@@ -56867,6 +57826,9 @@
       <c r="BF320" t="n">
         <v>753</v>
       </c>
+      <c r="BG320" t="n">
+        <v>756379</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="n">
@@ -57043,6 +58005,9 @@
       <c r="BF321" t="n">
         <v>699</v>
       </c>
+      <c r="BG321" t="n">
+        <v>749505</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="n">
@@ -57219,6 +58184,9 @@
       <c r="BF322" t="n">
         <v>857</v>
       </c>
+      <c r="BG322" t="n">
+        <v>797537</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="n">
@@ -57395,6 +58363,9 @@
       <c r="BF323" t="n">
         <v>834</v>
       </c>
+      <c r="BG323" t="n">
+        <v>767781</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="n">
@@ -57571,6 +58542,9 @@
       <c r="BF324" t="n">
         <v>795</v>
       </c>
+      <c r="BG324" t="n">
+        <v>757278</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="n">
@@ -57747,6 +58721,9 @@
       <c r="BF325" t="n">
         <v>843</v>
       </c>
+      <c r="BG325" t="n">
+        <v>760488</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="n">
@@ -57923,6 +58900,9 @@
       <c r="BF326" t="n">
         <v>815</v>
       </c>
+      <c r="BG326" t="n">
+        <v>688575</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="n">
@@ -58099,6 +59079,9 @@
       <c r="BF327" t="n">
         <v>658</v>
       </c>
+      <c r="BG327" t="n">
+        <v>688368</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="n">
@@ -58275,6 +59258,9 @@
       <c r="BF328" t="n">
         <v>618</v>
       </c>
+      <c r="BG328" t="n">
+        <v>679740</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="n">
@@ -58451,6 +59437,9 @@
       <c r="BF329" t="n">
         <v>812</v>
       </c>
+      <c r="BG329" t="n">
+        <v>733366</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="n">
@@ -58627,6 +59616,9 @@
       <c r="BF330" t="n">
         <v>779</v>
       </c>
+      <c r="BG330" t="n">
+        <v>751673</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="n">
@@ -58803,6 +59795,9 @@
       <c r="BF331" t="n">
         <v>801</v>
       </c>
+      <c r="BG331" t="n">
+        <v>751131</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="n">
@@ -58979,6 +59974,9 @@
       <c r="BF332" t="n">
         <v>886</v>
       </c>
+      <c r="BG332" t="n">
+        <v>735753</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="n">
@@ -59155,6 +60153,9 @@
       <c r="BF333" t="n">
         <v>917</v>
       </c>
+      <c r="BG333" t="n">
+        <v>703258</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="n">
@@ -59331,6 +60332,9 @@
       <c r="BF334" t="n">
         <v>656</v>
       </c>
+      <c r="BG334" t="n">
+        <v>679742</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="n">
@@ -59507,6 +60511,9 @@
       <c r="BF335" t="n">
         <v>606</v>
       </c>
+      <c r="BG335" t="n">
+        <v>650290</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="n">
@@ -59683,6 +60690,9 @@
       <c r="BF336" t="n">
         <v>807</v>
       </c>
+      <c r="BG336" t="n">
+        <v>720624</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="n">
@@ -59859,6 +60869,9 @@
       <c r="BF337" t="n">
         <v>814</v>
       </c>
+      <c r="BG337" t="n">
+        <v>734006</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="n">
@@ -60035,6 +61048,9 @@
       <c r="BF338" t="n">
         <v>775</v>
       </c>
+      <c r="BG338" t="n">
+        <v>754691</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="n">
@@ -60211,6 +61227,9 @@
       <c r="BF339" t="n">
         <v>917</v>
       </c>
+      <c r="BG339" t="n">
+        <v>749694</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="n">
@@ -60387,6 +61406,9 @@
       <c r="BF340" t="n">
         <v>928</v>
       </c>
+      <c r="BG340" t="n">
+        <v>725154</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="n">
@@ -60563,6 +61585,9 @@
       <c r="BF341" t="n">
         <v>741</v>
       </c>
+      <c r="BG341" t="n">
+        <v>700538</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="n">
@@ -60739,6 +61764,9 @@
       <c r="BF342" t="n">
         <v>690</v>
       </c>
+      <c r="BG342" t="n">
+        <v>700612</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="n">
@@ -60915,6 +61943,9 @@
       <c r="BF343" t="n">
         <v>791</v>
       </c>
+      <c r="BG343" t="n">
+        <v>761893</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="n">
@@ -61091,6 +62122,9 @@
       <c r="BF344" t="n">
         <v>797</v>
       </c>
+      <c r="BG344" t="n">
+        <v>756441</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="n">
@@ -61267,6 +62301,9 @@
       <c r="BF345" t="n">
         <v>915</v>
       </c>
+      <c r="BG345" t="n">
+        <v>787130</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="n">
@@ -61443,6 +62480,9 @@
       <c r="BF346" t="n">
         <v>1047</v>
       </c>
+      <c r="BG346" t="n">
+        <v>771614</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="n">
@@ -61619,6 +62659,9 @@
       <c r="BF347" t="n">
         <v>1039</v>
       </c>
+      <c r="BG347" t="n">
+        <v>750218</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="n">
@@ -61795,6 +62838,9 @@
       <c r="BF348" t="n">
         <v>900</v>
       </c>
+      <c r="BG348" t="n">
+        <v>736496</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="n">
@@ -61971,6 +63017,9 @@
       <c r="BF349" t="n">
         <v>832</v>
       </c>
+      <c r="BG349" t="n">
+        <v>719956</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="n">
@@ -62147,6 +63196,9 @@
       <c r="BF350" t="n">
         <v>1031</v>
       </c>
+      <c r="BG350" t="n">
+        <v>783211</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="n">
@@ -62323,6 +63375,9 @@
       <c r="BF351" t="n">
         <v>1014</v>
       </c>
+      <c r="BG351" t="n">
+        <v>780666</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="n">
@@ -62499,6 +63554,9 @@
       <c r="BF352" t="n">
         <v>1175</v>
       </c>
+      <c r="BG352" t="n">
+        <v>782209</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="n">
@@ -62675,6 +63733,9 @@
       <c r="BF353" t="n">
         <v>1309</v>
       </c>
+      <c r="BG353" t="n">
+        <v>770808</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="n">
@@ -62851,6 +63912,9 @@
       <c r="BF354" t="n">
         <v>1380</v>
       </c>
+      <c r="BG354" t="n">
+        <v>720703</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="n">
@@ -63027,6 +64091,9 @@
       <c r="BF355" t="n">
         <v>1040</v>
       </c>
+      <c r="BG355" t="n">
+        <v>698044</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="n">
@@ -63203,6 +64270,9 @@
       <c r="BF356" t="n">
         <v>984</v>
       </c>
+      <c r="BG356" t="n">
+        <v>694877</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="n">
@@ -63379,6 +64449,9 @@
       <c r="BF357" t="n">
         <v>1381</v>
       </c>
+      <c r="BG357" t="n">
+        <v>734873</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="n">
@@ -63555,6 +64628,9 @@
       <c r="BF358" t="n">
         <v>1263</v>
       </c>
+      <c r="BG358" t="n">
+        <v>722517</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="n">
@@ -63731,6 +64807,9 @@
       <c r="BF359" t="n">
         <v>1206</v>
       </c>
+      <c r="BG359" t="n">
+        <v>700034</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="n">
@@ -63907,6 +64986,9 @@
       <c r="BF360" t="n">
         <v>1166</v>
       </c>
+      <c r="BG360" t="n">
+        <v>708378</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="n">
@@ -64083,6 +65165,9 @@
       <c r="BF361" t="n">
         <v>1207</v>
       </c>
+      <c r="BG361" t="n">
+        <v>690127</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="n">
@@ -64259,6 +65344,9 @@
       <c r="BF362" t="n">
         <v>1125</v>
       </c>
+      <c r="BG362" t="n">
+        <v>675704</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="n">
@@ -64435,6 +65523,9 @@
       <c r="BF363" t="n">
         <v>1025</v>
       </c>
+      <c r="BG363" t="n">
+        <v>650223</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="n">
@@ -64611,6 +65702,9 @@
       <c r="BF364" t="n">
         <v>1161</v>
       </c>
+      <c r="BG364" t="n">
+        <v>638323</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="n">
@@ -64787,6 +65881,9 @@
       <c r="BF365" t="n">
         <v>845</v>
       </c>
+      <c r="BG365" t="n">
+        <v>556514</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="n">
@@ -64962,6 +66059,9 @@
       </c>
       <c r="BF366" t="n">
         <v>723</v>
+      </c>
+      <c r="BG366" t="n">
+        <v>327025</v>
       </c>
     </row>
   </sheetData>
